--- a/usd_krw_3m.xlsx
+++ b/usd_krw_3m.xlsx
@@ -25,9 +25,6 @@
     <t>02:00 종가</t>
   </si>
   <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
     <t>2026-02-20</t>
   </si>
   <si>
@@ -209,6 +206,9 @@
   </si>
   <si>
     <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
   </si>
 </sst>
 </file>
@@ -386,190 +386,190 @@
               <c:strCache>
                 <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>2026-02-19</c:v>
+                  <c:v>2026-02-20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2026-02-20</c:v>
+                  <c:v>2026-02-23</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2026-02-23</c:v>
+                  <c:v>2026-02-24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2026-02-24</c:v>
+                  <c:v>2026-02-25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2026-02-25</c:v>
+                  <c:v>2026-02-26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2026-02-26</c:v>
+                  <c:v>2026-02-27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2026-02-27</c:v>
+                  <c:v>2026-03-03</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2026-03-03</c:v>
+                  <c:v>2026-03-04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2026-03-04</c:v>
+                  <c:v>2026-03-05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2026-03-05</c:v>
+                  <c:v>2026-03-06</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2026-03-06</c:v>
+                  <c:v>2026-03-09</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2026-03-09</c:v>
+                  <c:v>2026-03-10</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2026-03-10</c:v>
+                  <c:v>2026-03-11</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2026-03-11</c:v>
+                  <c:v>2026-03-12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2026-03-12</c:v>
+                  <c:v>2026-03-13</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2026-03-13</c:v>
+                  <c:v>2026-03-16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2026-03-16</c:v>
+                  <c:v>2026-03-17</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2026-03-17</c:v>
+                  <c:v>2026-03-18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2026-03-18</c:v>
+                  <c:v>2026-03-19</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2026-03-19</c:v>
+                  <c:v>2026-03-20</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2026-03-20</c:v>
+                  <c:v>2026-03-23</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2026-03-23</c:v>
+                  <c:v>2026-03-24</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2026-03-24</c:v>
+                  <c:v>2026-03-25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2026-03-25</c:v>
+                  <c:v>2026-03-26</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2026-03-26</c:v>
+                  <c:v>2026-03-27</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2026-03-27</c:v>
+                  <c:v>2026-03-30</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2026-03-30</c:v>
+                  <c:v>2026-03-31</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2026-03-31</c:v>
+                  <c:v>2026-04-01</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2026-04-01</c:v>
+                  <c:v>2026-04-02</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2026-04-02</c:v>
+                  <c:v>2026-04-03</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2026-04-03</c:v>
+                  <c:v>2026-04-06</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2026-04-06</c:v>
+                  <c:v>2026-04-07</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2026-04-07</c:v>
+                  <c:v>2026-04-08</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2026-04-08</c:v>
+                  <c:v>2026-04-09</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2026-04-09</c:v>
+                  <c:v>2026-04-10</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2026-04-10</c:v>
+                  <c:v>2026-04-13</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2026-04-13</c:v>
+                  <c:v>2026-04-14</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2026-04-14</c:v>
+                  <c:v>2026-04-15</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2026-04-15</c:v>
+                  <c:v>2026-04-16</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2026-04-16</c:v>
+                  <c:v>2026-04-17</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2026-04-17</c:v>
+                  <c:v>2026-04-20</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -581,190 +581,190 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>1445.5</c:v>
+                  <c:v>1446.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1446.6</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1440</c:v>
+                  <c:v>1442.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1442.5</c:v>
+                  <c:v>1429.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1429.4</c:v>
+                  <c:v>1425.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1425.8</c:v>
+                  <c:v>1439.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1439.7</c:v>
+                  <c:v>1466.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1466.1</c:v>
+                  <c:v>1476.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1476.2</c:v>
+                  <c:v>1468.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1468.1</c:v>
+                  <c:v>1476.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1476.4</c:v>
+                  <c:v>1495.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1495.5</c:v>
+                  <c:v>1469.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1469.2</c:v>
+                  <c:v>1466.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1466.5</c:v>
+                  <c:v>1481.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1481.2</c:v>
+                  <c:v>1493.7</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1493.7</c:v>
+                  <c:v>1497.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1497.5</c:v>
+                  <c:v>1493.6</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1493.6</c:v>
+                  <c:v>1483.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1483.1</c:v>
+                  <c:v>1501</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1501</c:v>
+                  <c:v>1500.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1500.6</c:v>
+                  <c:v>1517.3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1517.3</c:v>
+                  <c:v>1495.2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1495.2</c:v>
+                  <c:v>1499.7</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1499.7</c:v>
+                  <c:v>1507</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1507</c:v>
+                  <c:v>1508.9</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1508.9</c:v>
+                  <c:v>1515.7</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1515.7</c:v>
+                  <c:v>1530.1</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1530.1</c:v>
+                  <c:v>1501.3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1501.3</c:v>
+                  <c:v>1519.7</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1519.7</c:v>
+                  <c:v>1505.2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1505.2</c:v>
+                  <c:v>1506.3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1506.3</c:v>
+                  <c:v>1504.2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1504.2</c:v>
+                  <c:v>1470.6</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1470.6</c:v>
+                  <c:v>1482.5</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>1482.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1482.5</c:v>
+                  <c:v>1489.3</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1489.3</c:v>
+                  <c:v>1481.2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1481.2</c:v>
+                  <c:v>1474.2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1474.2</c:v>
+                  <c:v>1474.6</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1474.6</c:v>
+                  <c:v>1483.5</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1483.5</c:v>
+                  <c:v>1477.2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1477.2</c:v>
+                  <c:v>1468.5</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1468.5</c:v>
+                  <c:v>1476</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1476</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1481</c:v>
+                  <c:v>1484.5</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1484.5</c:v>
+                  <c:v>1472.5</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1472.5</c:v>
+                  <c:v>1473.6</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1473.6</c:v>
+                  <c:v>1479</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1479</c:v>
+                  <c:v>1483.3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1483.3</c:v>
+                  <c:v>1462.8</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1462.8</c:v>
+                  <c:v>1455.1</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1455.1</c:v>
+                  <c:v>1454</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1454</c:v>
+                  <c:v>1471.7</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1471.7</c:v>
+                  <c:v>1472.4</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1472.4</c:v>
+                  <c:v>1489.9</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1489.9</c:v>
+                  <c:v>1490.6</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1490.6</c:v>
+                  <c:v>1491</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1491</c:v>
+                  <c:v>1500.8</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1500.8</c:v>
+                  <c:v>1500.3</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1500.3</c:v>
+                  <c:v>1507.8</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1507.8</c:v>
+                  <c:v>1506.8</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1506.8</c:v>
+                  <c:v>1506.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -909,190 +909,190 @@
               <c:strCache>
                 <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>2026-02-19</c:v>
+                  <c:v>2026-02-20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2026-02-20</c:v>
+                  <c:v>2026-02-23</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2026-02-23</c:v>
+                  <c:v>2026-02-24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2026-02-24</c:v>
+                  <c:v>2026-02-25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2026-02-25</c:v>
+                  <c:v>2026-02-26</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2026-02-26</c:v>
+                  <c:v>2026-02-27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2026-02-27</c:v>
+                  <c:v>2026-03-03</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2026-03-03</c:v>
+                  <c:v>2026-03-04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2026-03-04</c:v>
+                  <c:v>2026-03-05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2026-03-05</c:v>
+                  <c:v>2026-03-06</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2026-03-06</c:v>
+                  <c:v>2026-03-09</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2026-03-09</c:v>
+                  <c:v>2026-03-10</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2026-03-10</c:v>
+                  <c:v>2026-03-11</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2026-03-11</c:v>
+                  <c:v>2026-03-12</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2026-03-12</c:v>
+                  <c:v>2026-03-13</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2026-03-13</c:v>
+                  <c:v>2026-03-16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2026-03-16</c:v>
+                  <c:v>2026-03-17</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2026-03-17</c:v>
+                  <c:v>2026-03-18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2026-03-18</c:v>
+                  <c:v>2026-03-19</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2026-03-19</c:v>
+                  <c:v>2026-03-20</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2026-03-20</c:v>
+                  <c:v>2026-03-23</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2026-03-23</c:v>
+                  <c:v>2026-03-24</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2026-03-24</c:v>
+                  <c:v>2026-03-25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2026-03-25</c:v>
+                  <c:v>2026-03-26</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2026-03-26</c:v>
+                  <c:v>2026-03-27</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2026-03-27</c:v>
+                  <c:v>2026-03-30</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2026-03-30</c:v>
+                  <c:v>2026-03-31</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2026-03-31</c:v>
+                  <c:v>2026-04-01</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2026-04-01</c:v>
+                  <c:v>2026-04-02</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2026-04-02</c:v>
+                  <c:v>2026-04-03</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2026-04-03</c:v>
+                  <c:v>2026-04-06</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2026-04-06</c:v>
+                  <c:v>2026-04-07</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2026-04-07</c:v>
+                  <c:v>2026-04-08</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2026-04-08</c:v>
+                  <c:v>2026-04-09</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2026-04-09</c:v>
+                  <c:v>2026-04-10</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2026-04-10</c:v>
+                  <c:v>2026-04-13</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2026-04-13</c:v>
+                  <c:v>2026-04-14</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2026-04-14</c:v>
+                  <c:v>2026-04-15</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2026-04-15</c:v>
+                  <c:v>2026-04-16</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2026-04-16</c:v>
+                  <c:v>2026-04-17</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2026-04-17</c:v>
+                  <c:v>2026-04-20</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2026-04-20</c:v>
+                  <c:v>2026-04-21</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2026-04-21</c:v>
+                  <c:v>2026-04-22</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2026-04-22</c:v>
+                  <c:v>2026-04-23</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2026-04-23</c:v>
+                  <c:v>2026-04-24</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2026-04-24</c:v>
+                  <c:v>2026-04-27</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2026-04-27</c:v>
+                  <c:v>2026-04-28</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2026-04-28</c:v>
+                  <c:v>2026-04-29</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2026-04-29</c:v>
+                  <c:v>2026-04-30</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2026-04-30</c:v>
+                  <c:v>2026-05-04</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>2026-05-04</c:v>
+                  <c:v>2026-05-06</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>2026-05-06</c:v>
+                  <c:v>2026-05-07</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>2026-05-07</c:v>
+                  <c:v>2026-05-08</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>2026-05-08</c:v>
+                  <c:v>2026-05-11</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>2026-05-11</c:v>
+                  <c:v>2026-05-12</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>2026-05-12</c:v>
+                  <c:v>2026-05-13</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>2026-05-13</c:v>
+                  <c:v>2026-05-14</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>2026-05-14</c:v>
+                  <c:v>2026-05-15</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2026-05-15</c:v>
+                  <c:v>2026-05-18</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2026-05-18</c:v>
+                  <c:v>2026-05-19</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>2026-05-19</c:v>
+                  <c:v>2026-05-20</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>2026-05-20</c:v>
+                  <c:v>2026-05-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1104,190 +1104,190 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="62"/>
                 <c:pt idx="0">
-                  <c:v>1448.9</c:v>
+                  <c:v>1446.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1446.6</c:v>
+                  <c:v>1442.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1442.9</c:v>
+                  <c:v>1441</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1441</c:v>
+                  <c:v>1427.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1427.8</c:v>
+                  <c:v>1433.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1433.5</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1440</c:v>
+                  <c:v>1485.7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1485.7</c:v>
+                  <c:v>1462.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1462.9</c:v>
+                  <c:v>1482.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1482.2</c:v>
+                  <c:v>1481.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1481.6</c:v>
+                  <c:v>1473.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1473.7</c:v>
+                  <c:v>1465.7</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1465.7</c:v>
+                  <c:v>1477</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1477</c:v>
+                  <c:v>1488.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>1497.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1491.9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1488.4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1500.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1495</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1504.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1486.7</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1499.9</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1501.7</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1508</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1511.4</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1518.2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1517</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1513.3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1510.6</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1511.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1509.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1501</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1474.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1483.5</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1482.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1472.7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1475.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1460</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1472.8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1480.8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1480.3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1479.2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1476.8</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1473.6</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1473.2</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>1488.5</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="48">
+                  <c:v>1477.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1478.4</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1449.4</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1456</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1462.3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1472.7</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1490.9</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1489.3</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1493.4</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1497.5</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>1491.9</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1488.4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1500.7</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1495</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1504.7</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1486.7</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1499.9</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1501.7</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1508</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1511.4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1518.2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1517</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1513.3</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1510.6</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1511.4</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1509.8</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1501</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1474.7</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1483.5</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1482.7</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1472.7</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1475.5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1460</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1472.8</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1480.8</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1480.3</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1479.2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1476.8</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1473.6</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1473.2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1488.5</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1477.5</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1478.4</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1449.4</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1456</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1462.3</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1472.7</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1490.9</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1489.3</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1493.4</c:v>
-                </c:pt>
                 <c:pt idx="58">
-                  <c:v>1497.5</c:v>
+                  <c:v>1492.9</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1492.9</c:v>
+                  <c:v>1508.7</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>1508.7</c:v>
+                  <c:v>1496.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1746,10 +1746,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>1445.5</v>
+        <v>1446.6</v>
       </c>
       <c r="C2" s="3">
-        <v>1448.9</v>
+        <v>1446.6</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1757,10 +1757,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>1446.6</v>
+        <v>1440</v>
       </c>
       <c r="C3" s="3">
-        <v>1446.6</v>
+        <v>1442.9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1768,10 +1768,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>1440</v>
+        <v>1442.5</v>
       </c>
       <c r="C4" s="3">
-        <v>1442.9</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1779,10 +1779,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>1442.5</v>
+        <v>1429.4</v>
       </c>
       <c r="C5" s="3">
-        <v>1441</v>
+        <v>1427.8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1790,10 +1790,10 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>1429.4</v>
+        <v>1425.8</v>
       </c>
       <c r="C6" s="3">
-        <v>1427.8</v>
+        <v>1433.5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1801,10 +1801,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1425.8</v>
+        <v>1439.7</v>
       </c>
       <c r="C7" s="3">
-        <v>1433.5</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1812,10 +1812,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>1439.7</v>
+        <v>1466.1</v>
       </c>
       <c r="C8" s="3">
-        <v>1440</v>
+        <v>1485.7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1823,10 +1823,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>1466.1</v>
+        <v>1476.2</v>
       </c>
       <c r="C9" s="3">
-        <v>1485.7</v>
+        <v>1462.9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1834,10 +1834,10 @@
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>1476.2</v>
+        <v>1468.1</v>
       </c>
       <c r="C10" s="3">
-        <v>1462.9</v>
+        <v>1482.2</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1845,10 +1845,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>1468.1</v>
+        <v>1476.4</v>
       </c>
       <c r="C11" s="3">
-        <v>1482.2</v>
+        <v>1481.6</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1856,10 +1856,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>1476.4</v>
+        <v>1495.5</v>
       </c>
       <c r="C12" s="3">
-        <v>1481.6</v>
+        <v>1473.7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1867,10 +1867,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>1495.5</v>
+        <v>1469.2</v>
       </c>
       <c r="C13" s="3">
-        <v>1473.7</v>
+        <v>1465.7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1878,10 +1878,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>1469.2</v>
+        <v>1466.5</v>
       </c>
       <c r="C14" s="3">
-        <v>1465.7</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1889,10 +1889,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>1466.5</v>
+        <v>1481.2</v>
       </c>
       <c r="C15" s="3">
-        <v>1477</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1900,10 +1900,10 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1481.2</v>
+        <v>1493.7</v>
       </c>
       <c r="C16" s="3">
-        <v>1488.5</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1911,10 +1911,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="3">
-        <v>1493.7</v>
+        <v>1497.5</v>
       </c>
       <c r="C17" s="3">
-        <v>1497.5</v>
+        <v>1491.9</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1922,10 +1922,10 @@
         <v>19</v>
       </c>
       <c r="B18" s="3">
-        <v>1497.5</v>
+        <v>1493.6</v>
       </c>
       <c r="C18" s="3">
-        <v>1491.9</v>
+        <v>1488.4</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1933,10 +1933,10 @@
         <v>20</v>
       </c>
       <c r="B19" s="3">
-        <v>1493.6</v>
+        <v>1483.1</v>
       </c>
       <c r="C19" s="3">
-        <v>1488.4</v>
+        <v>1500.7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1944,10 +1944,10 @@
         <v>21</v>
       </c>
       <c r="B20" s="3">
-        <v>1483.1</v>
+        <v>1501</v>
       </c>
       <c r="C20" s="3">
-        <v>1500.7</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1955,10 +1955,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="3">
-        <v>1501</v>
+        <v>1500.6</v>
       </c>
       <c r="C21" s="3">
-        <v>1495</v>
+        <v>1504.7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1966,10 +1966,10 @@
         <v>23</v>
       </c>
       <c r="B22" s="3">
-        <v>1500.6</v>
+        <v>1517.3</v>
       </c>
       <c r="C22" s="3">
-        <v>1504.7</v>
+        <v>1486.7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1977,10 +1977,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="3">
-        <v>1517.3</v>
+        <v>1495.2</v>
       </c>
       <c r="C23" s="3">
-        <v>1486.7</v>
+        <v>1499.9</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1988,10 +1988,10 @@
         <v>25</v>
       </c>
       <c r="B24" s="3">
-        <v>1495.2</v>
+        <v>1499.7</v>
       </c>
       <c r="C24" s="3">
-        <v>1499.9</v>
+        <v>1501.7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1999,10 +1999,10 @@
         <v>26</v>
       </c>
       <c r="B25" s="3">
-        <v>1499.7</v>
+        <v>1507</v>
       </c>
       <c r="C25" s="3">
-        <v>1501.7</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2010,10 +2010,10 @@
         <v>27</v>
       </c>
       <c r="B26" s="3">
-        <v>1507</v>
+        <v>1508.9</v>
       </c>
       <c r="C26" s="3">
-        <v>1508</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2021,10 +2021,10 @@
         <v>28</v>
       </c>
       <c r="B27" s="3">
-        <v>1508.9</v>
+        <v>1515.7</v>
       </c>
       <c r="C27" s="3">
-        <v>1511.4</v>
+        <v>1518.2</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2032,10 +2032,10 @@
         <v>29</v>
       </c>
       <c r="B28" s="3">
-        <v>1515.7</v>
+        <v>1530.1</v>
       </c>
       <c r="C28" s="3">
-        <v>1518.2</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2043,10 +2043,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="3">
-        <v>1530.1</v>
+        <v>1501.3</v>
       </c>
       <c r="C29" s="3">
-        <v>1517</v>
+        <v>1513.3</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2054,10 +2054,10 @@
         <v>31</v>
       </c>
       <c r="B30" s="3">
-        <v>1501.3</v>
+        <v>1519.7</v>
       </c>
       <c r="C30" s="3">
-        <v>1513.3</v>
+        <v>1510.6</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2065,10 +2065,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="3">
-        <v>1519.7</v>
+        <v>1505.2</v>
       </c>
       <c r="C31" s="3">
-        <v>1510.6</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2076,10 +2076,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="3">
-        <v>1505.2</v>
+        <v>1506.3</v>
       </c>
       <c r="C32" s="3">
-        <v>1511.4</v>
+        <v>1509.8</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2087,10 +2087,10 @@
         <v>34</v>
       </c>
       <c r="B33" s="3">
-        <v>1506.3</v>
+        <v>1504.2</v>
       </c>
       <c r="C33" s="3">
-        <v>1509.8</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2098,10 +2098,10 @@
         <v>35</v>
       </c>
       <c r="B34" s="3">
-        <v>1504.2</v>
+        <v>1470.6</v>
       </c>
       <c r="C34" s="3">
-        <v>1501</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2109,10 +2109,10 @@
         <v>36</v>
       </c>
       <c r="B35" s="3">
-        <v>1470.6</v>
+        <v>1482.5</v>
       </c>
       <c r="C35" s="3">
-        <v>1479.2</v>
+        <v>1474.7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2123,7 +2123,7 @@
         <v>1482.5</v>
       </c>
       <c r="C36" s="3">
-        <v>1474.7</v>
+        <v>1483.5</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2131,10 +2131,10 @@
         <v>38</v>
       </c>
       <c r="B37" s="3">
-        <v>1482.5</v>
+        <v>1489.3</v>
       </c>
       <c r="C37" s="3">
-        <v>1483.5</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2142,10 +2142,10 @@
         <v>39</v>
       </c>
       <c r="B38" s="3">
-        <v>1489.3</v>
+        <v>1481.2</v>
       </c>
       <c r="C38" s="3">
-        <v>1482.7</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2153,10 +2153,10 @@
         <v>40</v>
       </c>
       <c r="B39" s="3">
-        <v>1481.2</v>
+        <v>1474.2</v>
       </c>
       <c r="C39" s="3">
-        <v>1472.7</v>
+        <v>1475.5</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2164,10 +2164,10 @@
         <v>41</v>
       </c>
       <c r="B40" s="3">
-        <v>1474.2</v>
+        <v>1474.6</v>
       </c>
       <c r="C40" s="3">
-        <v>1475.5</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2175,10 +2175,10 @@
         <v>42</v>
       </c>
       <c r="B41" s="3">
-        <v>1474.6</v>
+        <v>1483.5</v>
       </c>
       <c r="C41" s="3">
-        <v>1479.2</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2186,10 +2186,10 @@
         <v>43</v>
       </c>
       <c r="B42" s="3">
-        <v>1483.5</v>
+        <v>1477.2</v>
       </c>
       <c r="C42" s="3">
-        <v>1460</v>
+        <v>1472.8</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2197,10 +2197,10 @@
         <v>44</v>
       </c>
       <c r="B43" s="3">
-        <v>1477.2</v>
+        <v>1468.5</v>
       </c>
       <c r="C43" s="3">
-        <v>1472.8</v>
+        <v>1480.8</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2208,10 +2208,10 @@
         <v>45</v>
       </c>
       <c r="B44" s="3">
-        <v>1468.5</v>
+        <v>1476</v>
       </c>
       <c r="C44" s="3">
-        <v>1480.8</v>
+        <v>1480.3</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2219,10 +2219,10 @@
         <v>46</v>
       </c>
       <c r="B45" s="3">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="C45" s="3">
-        <v>1480.3</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2230,10 +2230,10 @@
         <v>47</v>
       </c>
       <c r="B46" s="3">
-        <v>1481</v>
+        <v>1484.5</v>
       </c>
       <c r="C46" s="3">
-        <v>1479.2</v>
+        <v>1476.8</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2241,10 +2241,10 @@
         <v>48</v>
       </c>
       <c r="B47" s="3">
-        <v>1484.5</v>
+        <v>1472.5</v>
       </c>
       <c r="C47" s="3">
-        <v>1476.8</v>
+        <v>1473.6</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -2252,10 +2252,10 @@
         <v>49</v>
       </c>
       <c r="B48" s="3">
-        <v>1472.5</v>
+        <v>1473.6</v>
       </c>
       <c r="C48" s="3">
-        <v>1473.6</v>
+        <v>1473.2</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -2263,10 +2263,10 @@
         <v>50</v>
       </c>
       <c r="B49" s="3">
-        <v>1473.6</v>
+        <v>1479</v>
       </c>
       <c r="C49" s="3">
-        <v>1473.2</v>
+        <v>1488.5</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -2274,10 +2274,10 @@
         <v>51</v>
       </c>
       <c r="B50" s="3">
-        <v>1479</v>
+        <v>1483.3</v>
       </c>
       <c r="C50" s="3">
-        <v>1488.5</v>
+        <v>1477.5</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -2285,10 +2285,10 @@
         <v>52</v>
       </c>
       <c r="B51" s="3">
-        <v>1483.3</v>
+        <v>1462.8</v>
       </c>
       <c r="C51" s="3">
-        <v>1477.5</v>
+        <v>1478.4</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -2296,10 +2296,10 @@
         <v>53</v>
       </c>
       <c r="B52" s="3">
-        <v>1462.8</v>
+        <v>1455.1</v>
       </c>
       <c r="C52" s="3">
-        <v>1478.4</v>
+        <v>1449.4</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2307,10 +2307,10 @@
         <v>54</v>
       </c>
       <c r="B53" s="3">
-        <v>1455.1</v>
+        <v>1454</v>
       </c>
       <c r="C53" s="3">
-        <v>1449.4</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2318,10 +2318,10 @@
         <v>55</v>
       </c>
       <c r="B54" s="3">
-        <v>1454</v>
+        <v>1471.7</v>
       </c>
       <c r="C54" s="3">
-        <v>1456</v>
+        <v>1462.3</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2329,10 +2329,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="3">
-        <v>1471.7</v>
+        <v>1472.4</v>
       </c>
       <c r="C55" s="3">
-        <v>1462.3</v>
+        <v>1472.7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -2340,10 +2340,10 @@
         <v>57</v>
       </c>
       <c r="B56" s="3">
-        <v>1472.4</v>
+        <v>1489.9</v>
       </c>
       <c r="C56" s="3">
-        <v>1472.7</v>
+        <v>1490.9</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -2351,10 +2351,10 @@
         <v>58</v>
       </c>
       <c r="B57" s="3">
-        <v>1489.9</v>
+        <v>1490.6</v>
       </c>
       <c r="C57" s="3">
-        <v>1490.9</v>
+        <v>1489.3</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2362,10 +2362,10 @@
         <v>59</v>
       </c>
       <c r="B58" s="3">
-        <v>1490.6</v>
+        <v>1491</v>
       </c>
       <c r="C58" s="3">
-        <v>1489.3</v>
+        <v>1493.4</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2373,10 +2373,10 @@
         <v>60</v>
       </c>
       <c r="B59" s="3">
-        <v>1491</v>
+        <v>1500.8</v>
       </c>
       <c r="C59" s="3">
-        <v>1493.4</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2384,10 +2384,10 @@
         <v>61</v>
       </c>
       <c r="B60" s="3">
-        <v>1500.8</v>
+        <v>1500.3</v>
       </c>
       <c r="C60" s="3">
-        <v>1497.5</v>
+        <v>1492.9</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2395,10 +2395,10 @@
         <v>62</v>
       </c>
       <c r="B61" s="3">
-        <v>1500.3</v>
+        <v>1507.8</v>
       </c>
       <c r="C61" s="3">
-        <v>1492.9</v>
+        <v>1508.7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2406,10 +2406,10 @@
         <v>63</v>
       </c>
       <c r="B62" s="3">
-        <v>1507.8</v>
+        <v>1506.8</v>
       </c>
       <c r="C62" s="3">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2417,10 +2417,10 @@
         <v>64</v>
       </c>
       <c r="B63" s="3">
-        <v>1506.8</v>
+        <v>1506.1</v>
       </c>
       <c r="C63" s="4">
-        <v>1508.7</v>
+        <v>1496.7</v>
       </c>
     </row>
   </sheetData>
